--- a/artfynd/A 33364-2023 artfynd.xlsx
+++ b/artfynd/A 33364-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33364-2023 artfynd.xlsx
+++ b/artfynd/A 33364-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>99472861</v>
       </c>
       <c r="B2" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437715.3489677107</v>
+        <v>437715</v>
       </c>
       <c r="R2" t="n">
-        <v>6211686.735026865</v>
+        <v>6211686</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2022-03-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-03-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106901671</v>
+        <v>99472918</v>
       </c>
       <c r="B3" t="n">
-        <v>57587</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>57890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,36 +788,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100141</v>
+        <v>100082</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -845,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437702.2268438521</v>
+        <v>437702</v>
       </c>
       <c r="R3" t="n">
-        <v>6211708.147977876</v>
+        <v>6211710</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,27 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-04-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-04-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Funnen under bråte på avställningsplats bredvid vägen.</t>
+          <t>2022-03-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,22 +864,137 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>106901671</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58829</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100141</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Triturus cristatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Grönalundsvägen, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>437703</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6211708</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Önnestad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-04-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-04-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Funnen under bråte på avställningsplats bredvid vägen.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Jan Pröjts</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Jan Pröjts</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33364-2023 artfynd.xlsx
+++ b/artfynd/A 33364-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99472861</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99472918</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,8 +1010,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106901671</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>